--- a/数据导出/trigger_prototypes.xlsx
+++ b/数据导出/trigger_prototypes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,326 @@
         <v>46129.37647059297</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Ethernet has changed to lower speed than it was before</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:net.if.speed[node_exporter,"{#IFNAME}"].change()}&lt;0 and {Template OS Linux by Prom:net.if.speed[node_exporter,"{#IFNAME}"].last()}&gt;0
+and (
+{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=6 or
+{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=7 or
+{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=11 or
+{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=62 or
+{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=69 or
+{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=117
+)
+and
+({Template OS Linux by Prom:net.if.status[node_exporter,"{#IFNAME}"].last()}&lt;&gt;2)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Ethernet has changed to lower speed than it was before</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].change()}&lt;0 and {Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}&gt;0
+and
+({Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=6
+or {Template OS Linux by Prom:net.if.type[node_exporter,"{#IFNAME}"].last()}=1)
+and
+({Template OS Linux by Prom:net.if.status[node_exporter,"{#IFNAME}"].last()}&lt;&gt;2)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): High bandwidth usage (&gt;{$IF.UTIL.MAX:"{#IFNAME}"}%)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>({Template OS Linux by Prom:net.if.in[node_exporter,"{#IFNAME}"].avg(15m)}&gt;({$IF.UTIL.MAX:"{#IFNAME}"}/100)*{Template OS Linux by Prom:net.if.speed[node_exporter,"{#IFNAME}"].last()} or
+{Template OS Linux by Prom:net.if.out[node_exporter,"{#IFNAME}"].avg(15m)}&gt;({$IF.UTIL.MAX:"{#IFNAME}"}/100)*{Template OS Linux by Prom:net.if.speed[node_exporter,"{#IFNAME}"].last()}) and
+{Template OS Linux by Prom:net.if.speed[node_exporter,"{#IFNAME}"].last()}&gt;0</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): High error rate (&gt;{$IF.ERRORS.WARN:"{#IFNAME}"} for 5m)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:net.if.in.errors[node_exporter,"{#IFNAME}"].min(5m)}&gt;{$IF.ERRORS.WARN:"{#IFNAME}"}
+or {Template OS Linux by Prom:net.if.out.errors[node_exporter"{#IFNAME}"].min(5m)}&gt;{$IF.ERRORS.WARN:"{#IFNAME}"}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Link down</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{$IFCONTROL:"{#IFNAME}"}=1 and ({last()}=2 and {diff()}=1)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk read/write request responses are too high (read &gt; {$VFS.DEV.READ.AWAIT.WARN:"{#DEVNAME}"} ms for 15m or write &gt; {$VFS.DEV.WRITE.AWAIT.WARN:"{#DEVNAME}"} ms for 15m)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:vfs.dev.read.await[node_exporter,"{#DEVNAME}"].min(15m)} &gt; {$VFS.DEV.READ.AWAIT.WARN:"{#DEVNAME}"} or {Template OS Linux by Prom:vfs.dev.write.await[node_exporter,"{#DEVNAME}"].min(15m)} &gt; {$VFS.DEV.WRITE.AWAIT.WARN:"{#DEVNAME}"}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Disk space is critically low (used &gt; {$VFS.FS.PUSED.MAX.CRIT:"{#FSNAME}"}%)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:vfs.fs.pused[node_exporter,"{#FSNAME}"].last()}&gt;{$VFS.FS.PUSED.MAX.CRIT:"{#FSNAME}"} and
+(({Template OS Linux by Prom:vfs.fs.total[node_exporter,"{#FSNAME}"].last()}-{Template OS Linux by Prom:vfs.fs.used[node_exporter,"{#FSNAME}"].last()})&lt;{$VFS.FS.FREE.MIN.CRIT:"{#FSNAME}"} or {Template OS Linux by Prom:vfs.fs.pused[node_exporter,"{#FSNAME}"].timeleft(1h,,100)}&lt;1d)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Disk space is low (used &gt; {$VFS.FS.PUSED.MAX.WARN:"{#FSNAME}"}%)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{Template OS Linux by Prom:vfs.fs.pused[node_exporter,"{#FSNAME}"].last()}&gt;{$VFS.FS.PUSED.MAX.WARN:"{#FSNAME}"} and
+(({Template OS Linux by Prom:vfs.fs.total[node_exporter,"{#FSNAME}"].last()}-{Template OS Linux by Prom:vfs.fs.used[node_exporter,"{#FSNAME}"].last()})&lt;{$VFS.FS.FREE.MIN.WARN:"{#FSNAME}"} or {Template OS Linux by Prom:vfs.fs.pused[node_exporter,"{#FSNAME}"].timeleft(1h,,100)}&lt;1d)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Running out of free inodes (free &lt; {$VFS.FS.INODE.PFREE.MIN.CRIT:"{#FSNAME}"}%)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{min(5m)}&lt;{$VFS.FS.INODE.PFREE.MIN.CRIT:"{#FSNAME}"}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>50</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Running out of free inodes (free &lt; {$VFS.FS.INODE.PFREE.MIN.WARN:"{#FSNAME}"}%)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{min(5m)}&lt;{$VFS.FS.INODE.PFREE.MIN.WARN:"{#FSNAME}"}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
